--- a/outputs/reports/easy_ensemble/evaluation.xlsx
+++ b/outputs/reports/easy_ensemble/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7242611731360824</v>
+        <v>0.7546889820395924</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007444725717349827</v>
+        <v>0.01000263227165043</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7683397683397684</v>
+        <v>0.7608951707891637</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01474656654480782</v>
+        <v>0.01974569018217386</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7241424724381613</v>
+        <v>0.7546687642691327</v>
       </c>
       <c r="G2" t="n">
-        <v>208939</v>
+        <v>196678</v>
       </c>
       <c r="H2" t="n">
-        <v>79594</v>
+        <v>63937</v>
       </c>
       <c r="I2" t="n">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="J2" t="n">
-        <v>597</v>
+        <v>646</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8378898048866475</v>
+        <v>0.8490409780236461</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03159796651811853</v>
+        <v>0.04096584493647336</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,32 +562,47 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>상위1%양성포착비율(top_1pct_recall)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>상위5%건수(top_5pct_count)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>상위5%양성비율(top_5pct_positive_rate)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>상위5%리프트(top_5pct_lift)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>상위5%양성포착비율(top_5pct_recall)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>상위10%건수(top_10pct_count)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>상위10%양성비율(top_10pct_positive_rate)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>상위10%리프트(top_10pct_lift)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>상위10%양성포착비율(top_10pct_recall)</t>
         </is>
       </c>
     </row>
@@ -598,34 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002685700459714493</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
-        <v>2894</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06046993780234969</v>
+        <v>0.06806883365200765</v>
       </c>
       <c r="E2" t="n">
-        <v>22.51551828262264</v>
+        <v>20.96295585628802</v>
       </c>
       <c r="F2" t="n">
-        <v>14466</v>
+        <v>0.2096584216725559</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02274298354762892</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>8.468175765977508</v>
+        <v>0.02914180816888481</v>
       </c>
       <c r="I2" t="n">
-        <v>28931</v>
+        <v>8.974715819869608</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01489751477653728</v>
+        <v>0.4487632508833923</v>
       </c>
       <c r="K2" t="n">
-        <v>5.546975546975546</v>
+        <v>26147</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0182430106704402</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5.618245632433425</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.5618374558303887</v>
       </c>
     </row>
   </sheetData>
@@ -706,7 +730,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2360</v>
+        <v>2476</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -725,13 +749,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45495</v>
+        <v>47773</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001978239366963402</v>
+        <v>0.0001255939547443116</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -744,13 +768,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160389</v>
+        <v>145904</v>
       </c>
       <c r="C6" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001047453378972374</v>
+        <v>0.001288518477903279</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -763,13 +787,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76692</v>
+        <v>61999</v>
       </c>
       <c r="C7" t="n">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005020080321285141</v>
+        <v>0.007177535121534218</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -782,13 +806,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4191</v>
+        <v>3154</v>
       </c>
       <c r="C8" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04748270102600811</v>
+        <v>0.05928979074191503</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -801,13 +825,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08743169398907104</v>
+        <v>0.1455696202531646</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
